--- a/data-vh/Неделя_06.07-12.07_2026_ВХ.xlsx
+++ b/data-vh/Неделя_06.07-12.07_2026_ВХ.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F38800F-0310-451C-AF41-7BB5A08E271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705CD23E-FDFA-4DBD-9E0B-CBF05AD1091F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="102">
   <si>
     <t>№ п/п</t>
   </si>
@@ -82,9 +82,6 @@
     <t>_уу_Лист 4,0 ГОСТ 19903-2015/ Ст3сп, Ст3сп5, В-Ст3сп (С255, Ст2сп)</t>
   </si>
   <si>
-    <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
-  </si>
-  <si>
     <t>Подгиб</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
     <t>ГПЦ(закупка) Хомут трубостойки (от поставщика/переработчика)</t>
   </si>
   <si>
-    <t>Опоры по СТО 350</t>
-  </si>
-  <si>
     <t>Несоответствие геометрических размеров</t>
   </si>
   <si>
@@ -142,9 +136,6 @@
     <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-5,0 (Окно) (ЭЗ 354.00.00.000 СБ)  (от поставщика/перераб</t>
   </si>
   <si>
-    <t>Закладные ЗА и ЗФ</t>
-  </si>
-  <si>
     <t>Невыполнение требований НТД</t>
   </si>
   <si>
@@ -166,9 +157,6 @@
     <t>ГПОкр(210-240 мкм (RAL 6034)) Клин Ц 221.00.00.020</t>
   </si>
   <si>
-    <t>ДиМ</t>
-  </si>
-  <si>
     <t>1.Покрытие сплошное, темно серого цвета.    2.Включения отсутствуют.    3.Потеки, сморщивание отсутствуют.    4.На поверхности изделий имеются загрязнения неустановленной консистенции.    5.Толщина покрытия:    от 12  мкм до 57 мкм, ср.= 44 мкм.</t>
   </si>
   <si>
@@ -326,6 +314,18 @@
   </si>
   <si>
     <t>Переработчик</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Листы</t>
+  </si>
+  <si>
+    <t>ОО</t>
+  </si>
+  <si>
+    <t>МК, другое</t>
   </si>
 </sst>
 </file>
@@ -749,16 +749,16 @@
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" customWidth="1"/>
-    <col min="8" max="8" width="74.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="47.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.28515625" style="1" customWidth="1"/>
     <col min="12" max="12" width="35.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="30.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="1" customWidth="1"/>
     <col min="14" max="14" width="74.7109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="11.140625" style="1" customWidth="1"/>
   </cols>
@@ -777,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -836,22 +836,22 @@
         <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="J2" s="3">
         <v>332</v>
       </c>
-      <c r="K2" s="3">
-        <v>332</v>
+      <c r="K2" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="O2" s="5"/>
     </row>
@@ -860,28 +860,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J3" s="3">
         <v>162</v>
@@ -890,13 +890,13 @@
         <v>11.34</v>
       </c>
       <c r="L3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="O3" s="5"/>
     </row>
@@ -905,28 +905,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3">
         <v>40</v>
@@ -935,13 +935,13 @@
         <v>7320</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O4" s="5"/>
     </row>
@@ -950,26 +950,26 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3">
         <v>4</v>
@@ -978,13 +978,13 @@
         <v>5.72</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O5" s="5"/>
     </row>
@@ -993,26 +993,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J6" s="3">
         <v>1</v>
@@ -1021,13 +1021,13 @@
         <v>187.18</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O6" s="5"/>
     </row>
@@ -1036,26 +1036,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J7" s="3">
         <v>1</v>
@@ -1064,13 +1064,13 @@
         <v>31.33</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="O7" s="5"/>
     </row>
@@ -1079,26 +1079,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J8" s="3">
         <v>1</v>
@@ -1107,13 +1107,13 @@
         <v>27.07</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="O8" s="5"/>
     </row>
@@ -1122,26 +1122,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J9" s="3">
         <v>1</v>
@@ -1150,13 +1150,13 @@
         <v>23.52</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O9" s="5"/>
     </row>
@@ -1165,26 +1165,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J10" s="3">
         <v>1</v>
@@ -1193,13 +1193,13 @@
         <v>19.82</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O10" s="5"/>
     </row>
@@ -1208,26 +1208,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3">
         <v>1</v>
@@ -1236,13 +1236,13 @@
         <v>15.84</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="O11" s="5"/>
     </row>
@@ -1251,26 +1251,26 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3">
         <v>2</v>
@@ -1279,13 +1279,13 @@
         <v>191.68</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="O12" s="5"/>
     </row>
@@ -1294,26 +1294,26 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3">
         <v>4</v>
@@ -1322,13 +1322,13 @@
         <v>341.24</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O13" s="5"/>
     </row>
@@ -1337,26 +1337,26 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J14" s="3">
         <v>2</v>
@@ -1365,13 +1365,13 @@
         <v>29.56</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O14" s="5"/>
     </row>
@@ -1380,26 +1380,26 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J15" s="3">
         <v>2</v>
@@ -1408,13 +1408,13 @@
         <v>35.200000000000003</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O15" s="5"/>
     </row>
@@ -1423,26 +1423,26 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3">
         <v>2</v>
@@ -1451,13 +1451,13 @@
         <v>41.2</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O16" s="5"/>
     </row>
@@ -1466,26 +1466,26 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J17" s="3">
         <v>4</v>
@@ -1494,13 +1494,13 @@
         <v>24.48</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="O17" s="5"/>
     </row>
@@ -1509,26 +1509,26 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J18" s="3">
         <v>2</v>
@@ -1537,13 +1537,13 @@
         <v>10.62</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O18" s="5"/>
     </row>
@@ -1552,26 +1552,26 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J19" s="3">
         <v>1</v>
@@ -1580,13 +1580,13 @@
         <v>23.28</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O19" s="5"/>
     </row>
@@ -1595,26 +1595,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J20" s="3">
         <v>2</v>
@@ -1623,13 +1623,13 @@
         <v>3.74</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O20" s="5"/>
     </row>
@@ -1638,26 +1638,26 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J21" s="3">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>33.380000000000003</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O21" s="5"/>
     </row>
@@ -1681,26 +1681,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J22" s="3">
         <v>2</v>
@@ -1709,13 +1709,13 @@
         <v>48.32</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O22" s="5"/>
     </row>
@@ -1724,26 +1724,26 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J23" s="3">
         <v>2</v>
@@ -1752,13 +1752,13 @@
         <v>48.32</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O23" s="5"/>
     </row>
@@ -1767,26 +1767,26 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J24" s="3">
         <v>1</v>
@@ -1795,13 +1795,13 @@
         <v>590.32000000000005</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O24" s="5"/>
     </row>
@@ -1810,26 +1810,26 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J25" s="3">
         <v>2</v>
@@ -1838,13 +1838,13 @@
         <v>11.84</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O25" s="5"/>
     </row>
@@ -1853,26 +1853,26 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J26" s="3">
         <v>2</v>
@@ -1881,13 +1881,13 @@
         <v>11.84</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O26" s="5"/>
     </row>
@@ -1896,26 +1896,26 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J27" s="3">
         <v>2</v>
@@ -1924,13 +1924,13 @@
         <v>172.48</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O27" s="5"/>
     </row>
@@ -1939,26 +1939,26 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J28" s="3">
         <v>16</v>
@@ -1967,13 +1967,13 @@
         <v>1169.92</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O28" s="5"/>
     </row>
@@ -1982,26 +1982,26 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="J29" s="3">
         <v>16</v>
@@ -2010,13 +2010,13 @@
         <v>1169.92</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O29" s="5"/>
     </row>
